--- a/cosmos-graph/interim/Codelist_Coverage.xlsx
+++ b/cosmos-graph/interim/Codelist_Coverage.xlsx
@@ -484,7 +484,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-23 19:04</t>
+          <t>Generated: 2026-09-30 18:19</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Sources: COSMoS public exports + NCI EVS CT package 2026-03-27.</t>
+          <t>Sources: COSMoS public exports + NCI EVS CT package 2026-09-25.</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="E73" s="6" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>130</v>
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="E109" s="6" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>14</v>
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="E129" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>1</v>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="E130" s="6" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>20</v>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="E135" s="6" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>38</v>
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="E136" s="6" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>38</v>
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="E137" s="6" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>38</v>
@@ -7376,7 +7376,7 @@
         </is>
       </c>
       <c r="E157" s="6" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>199</v>
@@ -8594,7 +8594,7 @@
         </is>
       </c>
       <c r="E186" s="6" t="n">
-        <v>2505</v>
+        <v>2513</v>
       </c>
       <c r="F186" s="6" t="n">
         <v>147</v>
@@ -8636,7 +8636,7 @@
         </is>
       </c>
       <c r="E187" s="6" t="n">
-        <v>2505</v>
+        <v>2513</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>147</v>
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="E188" s="6" t="n">
-        <v>1474</v>
+        <v>1481</v>
       </c>
       <c r="F188" s="6" t="n">
         <v>133</v>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="E191" s="6" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F191" s="6" t="n">
         <v>14</v>
@@ -8846,7 +8846,7 @@
         </is>
       </c>
       <c r="E192" s="6" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F192" s="6" t="n">
         <v>14</v>
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="E194" s="6" t="n">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="F194" s="6" t="n">
         <v>451</v>
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="E197" s="6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F197" s="6" t="n">
         <v>7</v>
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="E202" s="6" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F202" s="6" t="n">
         <v>50</v>
@@ -9308,7 +9308,7 @@
         </is>
       </c>
       <c r="E203" s="6" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F203" s="6" t="n">
         <v>50</v>
@@ -9854,7 +9854,7 @@
         </is>
       </c>
       <c r="E216" s="6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F216" s="6" t="n">
         <v>14</v>
@@ -10148,7 +10148,7 @@
         </is>
       </c>
       <c r="E223" s="6" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F223" s="6" t="n">
         <v>26</v>
@@ -10652,7 +10652,7 @@
         </is>
       </c>
       <c r="E235" s="6" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F235" s="6" t="n">
         <v>17</v>
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="E237" s="6" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F237" s="6" t="n">
         <v>135</v>
@@ -10770,7 +10770,7 @@
         </is>
       </c>
       <c r="E238" s="6" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F238" s="6" t="n">
         <v>135</v>
@@ -10812,7 +10812,7 @@
         </is>
       </c>
       <c r="E239" s="6" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F239" s="6" t="n">
         <v>8</v>
@@ -10854,7 +10854,7 @@
         </is>
       </c>
       <c r="E240" s="6" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F240" s="6" t="n">
         <v>94</v>
@@ -10896,7 +10896,7 @@
         </is>
       </c>
       <c r="E241" s="6" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F241" s="6" t="n">
         <v>94</v>
@@ -11148,7 +11148,7 @@
         </is>
       </c>
       <c r="E247" s="6" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F247" s="6" t="n">
         <v>75</v>
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="E248" s="6" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F248" s="6" t="n">
         <v>75</v>
@@ -12618,7 +12618,7 @@
         </is>
       </c>
       <c r="E282" s="6" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F282" s="6" t="n">
         <v>9</v>
@@ -12660,7 +12660,7 @@
         </is>
       </c>
       <c r="E283" s="6" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F283" s="6" t="n">
         <v>9</v>
@@ -12786,7 +12786,7 @@
         </is>
       </c>
       <c r="E286" s="6" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F286" s="6" t="n">
         <v>129</v>
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="E287" s="6" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F287" s="6" t="n">
         <v>129</v>
@@ -13248,7 +13248,7 @@
         </is>
       </c>
       <c r="E297" s="6" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F297" s="6" t="n">
         <v>78</v>
@@ -13290,7 +13290,7 @@
         </is>
       </c>
       <c r="E298" s="6" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F298" s="6" t="n">
         <v>78</v>
